--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575030489</v>
+        <v>46157.93119177812</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119177812</v>
+        <v>46157.93184539967</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184539967</v>
+        <v>46157.93406421163</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406421163</v>
+        <v>46157.93724452454</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724452454</v>
+        <v>46158.28222148884</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222148884</v>
+        <v>46158.29703642623</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29703642623</v>
+        <v>46158.29822019377</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822019377</v>
+        <v>46158.33393107237</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393107237</v>
+        <v>46158.36862892756</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Тошпулатов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862892756</v>
+        <v>46158.37293859985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
